--- a/cache_proyectos/barnes_noble/takeoff_work/etapas/8_excel/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
+++ b/cache_proyectos/barnes_noble/takeoff_work/etapas/8_excel/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
@@ -1600,7 +1600,7 @@
     <t xml:space="preserve">CLOSED - estimator decision 2026-10-27: FRP-1 in our scope. N/SHEET: A-510; 1-4/A-226B; 9-12/A-200.</t>
   </si>
   <si>
-    <t xml:space="preserve">Applied: FRP + 1,030.64 SF (Cafe Work Room 875.20 + Janitor 155.44) + PVC trim (J-mold top / bottom + inside corners).</t>
+    <t xml:space="preserve">Applied: FRP + 1,030.64 SF (Cafe Work Room 875.20 + Janitor 155.44) + PVC trim (J-mold top / bottom + inside corners). Revised by RFI-55 (estimator decision 2026-10-28): Work Room FRP 852.20 SF (finished dimensions, 1/A-221); PVC trim per real corners / edges + division bars.</t>
   </si>
   <si>
     <t xml:space="preserve">RFI-14</t>
@@ -1678,7 +1678,7 @@
     <t xml:space="preserve">CLOSED - estimator decision 2026-10-27: One face of types 3 / 4 (122.32 LF) = 5/8" FRT plywood + FRP (A-410 building dept note: all plywood FRT). N/SHEET: 3/A-410; 4/A-410.</t>
   </si>
   <si>
-    <t xml:space="preserve">Applied: 5/8" FRT plywood + 936.74 SF, FRP + 936.74 SF, 5/8" Type X - 936.74 SF on that face, PVC trim + 244.64 LF.</t>
+    <t xml:space="preserve">Applied: 5/8" FRT plywood + 936.74 SF, FRP + 936.74 SF, 5/8" Type X - 936.74 SF on that face, PVC trim + 244.64 LF. Revised by RFI-55 (estimator decision 2026-10-28): types 3 / 4 PVC 154.32 LF (hourglass cap corners take the metal corner guard) + division bars 167 LF.</t>
   </si>
   <si>
     <t xml:space="preserve">RFI-23</t>

--- a/cache_proyectos/barnes_noble/takeoff_work/etapas/8_excel/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
+++ b/cache_proyectos/barnes_noble/takeoff_work/etapas/8_excel/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
@@ -2281,7 +2281,7 @@
     <t xml:space="preserve">reglas.py compuerta OK</t>
   </si>
   <si>
-    <t xml:space="preserve">{"canon": "f3623ea48012f20791133dc93e86ea7c66aaa059d25e649d281e1ec80dbfdf87", "evidencias": "82f4ec13c901d7191f9772989e98854d158340ab19499f6cfbada96ca6cbd21e", "familias_out": "b185337f275b61687384e9e03306738f9c81a7254fdb31cb674cf3d3b32b5c00", "reglas": "26cd43ad2b0dabf9c000cc5efad076b676363c3a45b7af4570136de43fd09305", "version": "v73"}</t>
+    <t xml:space="preserve">{"canon": "c7127044ce1e61197dce878326d3f645ed6b2bbe7ae262f4e911ae5ab5a71334", "evidencias": "82f4ec13c901d7191f9772989e98854d158340ab19499f6cfbada96ca6cbd21e", "familias_out": "b185337f275b61687384e9e03306738f9c81a7254fdb31cb674cf3d3b32b5c00", "reglas": "26cd43ad2b0dabf9c000cc5efad076b676363c3a45b7af4570136de43fd09305", "version": "v73"}</t>
   </si>
 </sst>
 </file>
